--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/04_İç Tetkik ve İyileştirme/EKG-KLT-PLN-04_yillik_ic_tetkik_programi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/04_İç Tetkik ve İyileştirme/EKG-KLT-PLN-04_yillik_ic_tetkik_programi.xlsx
@@ -995,7 +995,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Yıllık İç Tetkik Programı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b7a1e85a15d47e2"/>
   <x:tableParts count="1">
@@ -1187,7 +1188,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Yıllık İç Tetkik Programı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8b91427fbd5427c"/>
   <x:tableParts count="1">
@@ -1482,7 +1484,8 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <x:oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-PLN-04&amp;C&amp;"Arial,Regular"&amp;11Yıllık İç Tetkik Programı</x:oddHeader>
-    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
+    <x:oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 01.06.2026 | Revizyon: 31.08.2026
+Revizyon nedeni: Doküman kimliği ve ana liste ile tarih eşleşmesi güncellendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</x:oddFooter>
   </x:headerFooter>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c2ef19b35704684"/>
   <x:tableParts count="1">
